--- a/data/trans_orig/IP31KM13_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM13_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,69 +725,69 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69341</t>
+          <t>54185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71400</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>54600</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53264</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54922</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>99,41%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>96,98%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>72446</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>66879</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>74607</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>182</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>143425</t>
+          <t>112987</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137915</t>
+          <t>107923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145587</t>
+          <t>114856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7728</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>93072</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>84086</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>100494</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>101274</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>89411</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>114307</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>102061</t>
+          <t>76920</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92660</t>
+          <t>68519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110072</t>
+          <t>83658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>203334</t>
+          <t>169992</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187316</t>
+          <t>158401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>218554</t>
+          <t>179958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21879</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14457</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30865</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24375</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11342</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36238</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>30814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>48737</t>
+          <t>44292</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33517</t>
+          <t>34326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64755</t>
+          <t>55883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56389</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54446</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49581</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45514</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52970</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63535</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60736</t>
+          <t>43935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>51470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>113115</t>
+          <t>104711</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107893</t>
+          <t>100016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116546</t>
+          <t>108091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2853</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5971</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10038</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,74 +1749,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56434</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34978</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>66063</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>66562</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>62463</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>68841</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>67223</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62679</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>69610</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>88,96%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>98,79%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>60260</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>33566</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>72053</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>44,54%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>147</t>
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>126822</t>
+          <t>123657</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>97464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138580</t>
+          <t>134424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13382</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34838</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>49,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>841</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7219</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7783</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>15107</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3314</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>41801</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>16621</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38993</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36593</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33214</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31089</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>34339</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31529</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>89,14%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40141</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>37800</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>135</t>
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>73332</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74473</t>
+          <t>74468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2986</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,74 +2435,74 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>46008</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42866</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>43228</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>40690</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>43161</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>40714</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>44286</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>52460</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>49673</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>53782</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>92,36%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>157</t>
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95688</t>
+          <t>89169</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92069</t>
+          <t>85874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97389</t>
+          <t>90889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>130562</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>124597</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>134728</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>115902</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>109965</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>119376</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>144426</t>
+          <t>113660</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137908</t>
+          <t>107798</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149461</t>
+          <t>117703</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>260328</t>
+          <t>244223</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>251892</t>
+          <t>236741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>266996</t>
+          <t>250062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>15974</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>7794</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>13731</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>146168</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>139069</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>151081</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>93,02%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>122413</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>117168</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>125292</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>143866</t>
+          <t>131578</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137223</t>
+          <t>125803</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148600</t>
+          <t>134776</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>266277</t>
+          <t>277746</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>258502</t>
+          <t>269409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272216</t>
+          <t>284125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10968</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6055</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>18067</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>6252</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3373</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>11497</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>25627</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>626011</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>595829</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>640733</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>603153</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>586492</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>613665</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>638897</t>
+          <t>557527</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>695737</t>
+          <t>579751</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1282346</t>
+          <t>1195814</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1247065</t>
+          <t>1168873</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1302456</t>
+          <t>1214604</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>60813</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>46091</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>90995</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>39469</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>66642</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105836</t>
+          <t>60681</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>115521</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95411</t>
+          <t>90427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>150802</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
